--- a/code-analysis/word-count-deep-dives/Deep-dives-word-counts.xlsx
+++ b/code-analysis/word-count-deep-dives/Deep-dives-word-counts.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mark/Documents/Files/Websites/Repositories/bbcelite-scripts/code-analysis/word-count-deep-dives/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1189DB4-C3F9-1A45-82FD-D124F85DC0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00941E6-9178-9948-860E-1C5748E1770C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15540" yWindow="2540" windowWidth="19940" windowHeight="17440" xr2:uid="{B861FA09-B3AD-9448-956B-DECF27F030C1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="297">
   <si>
     <t>Elite</t>
   </si>
@@ -848,9 +848,6 @@
     <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/the_custom_screen_mode.html</t>
   </si>
   <si>
-    <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/object_spawning.html</t>
-  </si>
-  <si>
     <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/panning_and_hardware_scrolling.html</t>
   </si>
   <si>
@@ -863,27 +860,15 @@
     <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/3d_object_definitions.html</t>
   </si>
   <si>
-    <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/the_visibility_table.html</t>
-  </si>
-  <si>
     <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/drawing_the_landscape_preview.html</t>
   </si>
   <si>
-    <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/3d_text_using_blocks.html</t>
-  </si>
-  <si>
     <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/the_drawing_tables.html</t>
   </si>
   <si>
-    <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/calculating_angles_for_the_landscape_view.html</t>
-  </si>
-  <si>
     <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/anti-cracker_checks.html</t>
   </si>
   <si>
-    <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/drawing_objects.html</t>
-  </si>
-  <si>
     <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/stacking_objects.html</t>
   </si>
   <si>
@@ -896,18 +881,12 @@
     <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/random_number_generation.html</t>
   </si>
   <si>
-    <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/calculating_gaze.html</t>
-  </si>
-  <si>
     <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/the_scanner.html</t>
   </si>
   <si>
     <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/the_key_logger.html</t>
   </si>
   <si>
-    <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/game_timings.html</t>
-  </si>
-  <si>
     <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/drawing_filled_polygons.html</t>
   </si>
   <si>
@@ -924,6 +903,30 @@
   </si>
   <si>
     <t>The Sentinel</t>
+  </si>
+  <si>
+    <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/object_management.html</t>
+  </si>
+  <si>
+    <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/drawing_3d_text_using_blocks.html</t>
+  </si>
+  <si>
+    <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/drawing_3d_objects.html</t>
+  </si>
+  <si>
+    <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/calculating_angles_for_drawing_3d_objects.html</t>
+  </si>
+  <si>
+    <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/calculating_quadrants_for_the_landscape_view.html</t>
+  </si>
+  <si>
+    <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/ray-casting_for_the_tile_visibility_table.html</t>
+  </si>
+  <si>
+    <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/following_the_gaze_vector.html</t>
+  </si>
+  <si>
+    <t>/Users/Mark/Sites/bbcelite-websites/thesentinel.bbcelite.com/deep_dives/enemy_timers_and_state_variables.html</t>
   </si>
 </sst>
 </file>
@@ -1323,7 +1326,7 @@
       </c>
       <c r="C2" s="6">
         <f>B2/$B$8</f>
-        <v>0.49083432538198324</v>
+        <v>0.41808589461879736</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1332,24 +1335,24 @@
       </c>
       <c r="B3" s="4">
         <f>SUMIF(wordcount.txt!B:B,"*revs.bbcelite.com*",wordcount.txt!A:A)</f>
-        <v>125448</v>
+        <v>125524</v>
       </c>
       <c r="C3" s="6">
         <f>B3/$B$8</f>
-        <v>0.26811601946623864</v>
+        <v>0.22851587745152477</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B4" s="4">
         <f>SUMIF(wordcount.txt!B:B,"*thesentinel.bbcelite.com*",wordcount.txt!A:A)</f>
-        <v>34649</v>
+        <v>116022</v>
       </c>
       <c r="C4" s="6">
         <f>B4/$B$8</f>
-        <v>7.4054205395747266E-2</v>
+        <v>0.21121752918709413</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1358,11 +1361,11 @@
       </c>
       <c r="B5" s="4">
         <f>SUMIF(wordcount.txt!B:B,"*aviator.bbcelite.com*",wordcount.txt!A:A)</f>
-        <v>41392</v>
+        <v>41357</v>
       </c>
       <c r="C5" s="6">
         <f>B5/$B$8</f>
-        <v>8.8465804777649301E-2</v>
+        <v>7.5290232495480613E-2</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1375,7 +1378,7 @@
       </c>
       <c r="C6" s="6">
         <f>B6/$B$8</f>
-        <v>7.8529644978381538E-2</v>
+        <v>6.6890466247103139E-2</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1387,7 +1390,7 @@
       </c>
       <c r="B8" s="5">
         <f>SUM(B2:B6)</f>
-        <v>467887</v>
+        <v>549301</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1403,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB40F6A-245F-024F-9684-E7DD745D31B2}">
-  <dimension ref="A1:B287"/>
+  <dimension ref="A1:B288"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.1640625" style="1" bestFit="1" customWidth="1"/>
@@ -2700,7 +2703,7 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
-        <v>1848</v>
+        <v>1851</v>
       </c>
       <c r="B162" t="s">
         <v>146</v>
@@ -2716,7 +2719,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
-        <v>1629</v>
+        <v>1656</v>
       </c>
       <c r="B164" t="s">
         <v>149</v>
@@ -2748,7 +2751,7 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
-        <v>1320</v>
+        <v>1366</v>
       </c>
       <c r="B168" t="s">
         <v>153</v>
@@ -2884,7 +2887,7 @@
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
-        <v>2508</v>
+        <v>2502</v>
       </c>
       <c r="B185" t="s">
         <v>169</v>
@@ -2900,7 +2903,7 @@
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="B187" t="s">
         <v>172</v>
@@ -2932,7 +2935,7 @@
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
-        <v>1368</v>
+        <v>1358</v>
       </c>
       <c r="B191" t="s">
         <v>176</v>
@@ -2964,7 +2967,7 @@
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="B195" t="s">
         <v>180</v>
@@ -2988,7 +2991,7 @@
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
-        <v>1258</v>
+        <v>1250</v>
       </c>
       <c r="B198" t="s">
         <v>183</v>
@@ -3036,7 +3039,7 @@
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B204" t="s">
         <v>189</v>
@@ -3052,7 +3055,7 @@
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B206" t="s">
         <v>191</v>
@@ -3116,7 +3119,7 @@
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B214" t="s">
         <v>199</v>
@@ -3124,585 +3127,593 @@
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
-        <v>4347</v>
+        <v>6328</v>
       </c>
       <c r="B215" t="s">
-        <v>244</v>
+        <v>276</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
-        <v>3269</v>
+        <v>6004</v>
       </c>
       <c r="B216" t="s">
-        <v>245</v>
+        <v>279</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
-        <v>2225</v>
+        <v>4992</v>
       </c>
       <c r="B217" t="s">
-        <v>246</v>
+        <v>295</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
-        <v>1951</v>
+        <v>4682</v>
       </c>
       <c r="B218" t="s">
-        <v>247</v>
+        <v>294</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
-        <v>1702</v>
+        <v>4408</v>
       </c>
       <c r="B219" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
-        <v>1505</v>
+        <v>3948</v>
       </c>
       <c r="B220" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
-        <v>1492</v>
+        <v>3804</v>
       </c>
       <c r="B221" t="s">
-        <v>250</v>
+        <v>293</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
-        <v>1474</v>
+        <v>3788</v>
       </c>
       <c r="B222" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
-        <v>1270</v>
+        <v>3655</v>
       </c>
       <c r="B223" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
-        <v>1253</v>
+        <v>3345</v>
       </c>
       <c r="B224" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
-        <v>1223</v>
+        <v>3118</v>
       </c>
       <c r="B225" t="s">
-        <v>254</v>
+        <v>290</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
-        <v>1188</v>
+        <v>3080</v>
       </c>
       <c r="B226" t="s">
-        <v>255</v>
+        <v>289</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
-        <v>1166</v>
+        <v>3046</v>
       </c>
       <c r="B227" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
-        <v>1097</v>
+        <v>2922</v>
       </c>
       <c r="B228" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
-        <v>1069</v>
+        <v>2852</v>
       </c>
       <c r="B229" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
-        <v>1015</v>
+        <v>2799</v>
       </c>
       <c r="B230" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
-        <v>943</v>
+        <v>2391</v>
       </c>
       <c r="B231" t="s">
-        <v>260</v>
+        <v>291</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
-        <v>861</v>
+        <v>2345</v>
       </c>
       <c r="B232" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
-        <v>664</v>
+        <v>2248</v>
       </c>
       <c r="B233" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
-        <v>626</v>
+        <v>2225</v>
       </c>
       <c r="B234" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
-        <v>575</v>
+        <v>2034</v>
       </c>
       <c r="B235" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
-        <v>520</v>
+        <v>2014</v>
       </c>
       <c r="B236" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
-        <v>283</v>
+        <v>1956</v>
       </c>
       <c r="B237" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
-        <v>271</v>
+        <v>1949</v>
       </c>
       <c r="B238" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
-        <v>186</v>
+        <v>1905</v>
       </c>
       <c r="B239" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
-        <v>184</v>
+        <v>1897</v>
       </c>
       <c r="B240" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
-        <v>180</v>
+        <v>1850</v>
       </c>
       <c r="B241" t="s">
-        <v>270</v>
+        <v>296</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
-        <v>129</v>
+        <v>1801</v>
       </c>
       <c r="B242" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
-        <v>115</v>
+        <v>1662</v>
       </c>
       <c r="B243" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
-        <v>105</v>
+        <v>1631</v>
       </c>
       <c r="B244" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
-        <v>95</v>
+        <v>1607</v>
       </c>
       <c r="B245" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
-        <v>91</v>
+        <v>1549</v>
       </c>
       <c r="B246" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
-        <v>90</v>
+        <v>1541</v>
       </c>
       <c r="B247" t="s">
-        <v>276</v>
+        <v>249</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
-        <v>89</v>
+        <v>1519</v>
       </c>
       <c r="B248" t="s">
-        <v>277</v>
+        <v>250</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
-        <v>87</v>
+        <v>1501</v>
       </c>
       <c r="B249" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
-        <v>86</v>
+        <v>1500</v>
       </c>
       <c r="B250" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
-        <v>86</v>
+        <v>1448</v>
       </c>
       <c r="B251" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
-        <v>85</v>
+        <v>1332</v>
       </c>
       <c r="B252" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
-        <v>84</v>
+        <v>1253</v>
       </c>
       <c r="B253" t="s">
-        <v>282</v>
+        <v>253</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
-        <v>83</v>
+        <v>1188</v>
       </c>
       <c r="B254" t="s">
-        <v>283</v>
+        <v>255</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
-        <v>83</v>
+        <v>1080</v>
       </c>
       <c r="B255" t="s">
-        <v>284</v>
+        <v>258</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
-        <v>82</v>
+        <v>1079</v>
       </c>
       <c r="B256" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
-        <v>82</v>
+        <v>1052</v>
       </c>
       <c r="B257" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
-        <v>81</v>
+        <v>1044</v>
       </c>
       <c r="B258" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
-        <v>81</v>
+        <v>1018</v>
       </c>
       <c r="B259" t="s">
-        <v>288</v>
+        <v>257</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
-        <v>81</v>
+        <v>976</v>
       </c>
       <c r="B260" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
-        <v>81</v>
+        <v>959</v>
       </c>
       <c r="B261" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
-        <v>81</v>
+        <v>943</v>
       </c>
       <c r="B262" t="s">
-        <v>291</v>
+        <v>260</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
-        <v>78</v>
+        <v>889</v>
       </c>
       <c r="B263" t="s">
-        <v>292</v>
+        <v>261</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
-        <v>78</v>
+        <v>664</v>
       </c>
       <c r="B264" t="s">
-        <v>293</v>
+        <v>262</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
-        <v>77</v>
+        <v>626</v>
       </c>
       <c r="B265" t="s">
-        <v>294</v>
+        <v>263</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
-        <v>3234</v>
+        <v>575</v>
       </c>
       <c r="B266" t="s">
-        <v>200</v>
+        <v>264</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
-        <v>3028</v>
+        <v>3234</v>
       </c>
       <c r="B267" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
-        <v>3015</v>
+        <v>3028</v>
       </c>
       <c r="B268" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
-        <v>2939</v>
+        <v>3015</v>
       </c>
       <c r="B269" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
-        <v>2845</v>
+        <v>2939</v>
       </c>
       <c r="B270" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
-        <v>2793</v>
+        <v>2845</v>
       </c>
       <c r="B271" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
-        <v>2606</v>
+        <v>2793</v>
       </c>
       <c r="B272" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
-        <v>2170</v>
+        <v>2606</v>
       </c>
       <c r="B273" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
-        <v>1924</v>
+        <v>2170</v>
       </c>
       <c r="B274" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
-        <v>1517</v>
+        <v>1924</v>
       </c>
       <c r="B275" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
-        <v>1490</v>
+        <v>1517</v>
       </c>
       <c r="B276" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
-        <v>1417</v>
+        <v>1490</v>
       </c>
       <c r="B277" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
-        <v>1385</v>
+        <v>1417</v>
       </c>
       <c r="B278" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
-        <v>1024</v>
+        <v>1385</v>
       </c>
       <c r="B279" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
-        <v>874</v>
+        <v>1024</v>
       </c>
       <c r="B280" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
-        <v>851</v>
+        <v>874</v>
       </c>
       <c r="B281" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
-        <v>799</v>
+        <v>851</v>
       </c>
       <c r="B282" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
-        <v>764</v>
+        <v>799</v>
       </c>
       <c r="B283" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
-        <v>665</v>
+        <v>764</v>
       </c>
       <c r="B284" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
-        <v>483</v>
+        <v>665</v>
       </c>
       <c r="B285" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
-        <v>468</v>
+        <v>483</v>
       </c>
       <c r="B286" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
+        <v>468</v>
+      </c>
+      <c r="B287" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A288" s="1">
         <v>452</v>
       </c>
-      <c r="B287" t="s">
+      <c r="B288" t="s">
         <v>221</v>
       </c>
     </row>

--- a/code-analysis/word-count-deep-dives/Deep-dives-word-counts.xlsx
+++ b/code-analysis/word-count-deep-dives/Deep-dives-word-counts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mark/Documents/Files/Websites/Repositories/bbcelite-scripts/code-analysis/word-count-deep-dives/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00941E6-9178-9948-860E-1C5748E1770C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4334C6B3-F0CE-8F4D-B2A5-1616DFD92500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15540" yWindow="2540" windowWidth="19940" windowHeight="17440" xr2:uid="{B861FA09-B3AD-9448-956B-DECF27F030C1}"/>
   </bookViews>
@@ -1322,11 +1322,11 @@
       </c>
       <c r="B2" s="4">
         <f>SUMIF(wordcount.txt!B:B,"*elite.bbcelite.com*",wordcount.txt!A:A)</f>
-        <v>229655</v>
+        <v>229851</v>
       </c>
       <c r="C2" s="6">
         <f>B2/$B$8</f>
-        <v>0.41808589461879736</v>
+        <v>0.41754271233548595</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1335,11 +1335,11 @@
       </c>
       <c r="B3" s="4">
         <f>SUMIF(wordcount.txt!B:B,"*revs.bbcelite.com*",wordcount.txt!A:A)</f>
-        <v>125524</v>
+        <v>126205</v>
       </c>
       <c r="C3" s="6">
         <f>B3/$B$8</f>
-        <v>0.22851587745152477</v>
+        <v>0.2292614694315013</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1348,11 +1348,11 @@
       </c>
       <c r="B4" s="4">
         <f>SUMIF(wordcount.txt!B:B,"*thesentinel.bbcelite.com*",wordcount.txt!A:A)</f>
-        <v>116022</v>
+        <v>116240</v>
       </c>
       <c r="C4" s="6">
         <f>B4/$B$8</f>
-        <v>0.21121752918709413</v>
+        <v>0.21115925047912296</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1361,11 +1361,11 @@
       </c>
       <c r="B5" s="4">
         <f>SUMIF(wordcount.txt!B:B,"*aviator.bbcelite.com*",wordcount.txt!A:A)</f>
-        <v>41357</v>
+        <v>41401</v>
       </c>
       <c r="C5" s="6">
         <f>B5/$B$8</f>
-        <v>7.5290232495480613E-2</v>
+        <v>7.5208225473900284E-2</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1374,11 +1374,11 @@
       </c>
       <c r="B6" s="4">
         <f>SUMIF(wordcount.txt!B:B,"*lander.bbcelite.com*",wordcount.txt!A:A)</f>
-        <v>36743</v>
+        <v>36788</v>
       </c>
       <c r="C6" s="6">
         <f>B6/$B$8</f>
-        <v>6.6890466247103139E-2</v>
+        <v>6.6828342279989461E-2</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B8" s="5">
         <f>SUM(B2:B6)</f>
-        <v>549301</v>
+        <v>550485</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1463,7 +1463,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>3370</v>
+        <v>3402</v>
       </c>
       <c r="B7" t="s">
         <v>223</v>
@@ -1471,7 +1471,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>3191</v>
+        <v>3201</v>
       </c>
       <c r="B8" t="s">
         <v>238</v>
@@ -1511,7 +1511,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>2862</v>
+        <v>2863</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>2817</v>
+        <v>2826</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
@@ -1559,7 +1559,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>2638</v>
+        <v>2650</v>
       </c>
       <c r="B19" t="s">
         <v>18</v>
@@ -1575,18 +1575,18 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>2582</v>
+        <v>2607</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>2569</v>
+        <v>2582</v>
       </c>
       <c r="B22" t="s">
-        <v>240</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -1703,7 +1703,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
-        <v>2097</v>
+        <v>2134</v>
       </c>
       <c r="B37" t="s">
         <v>227</v>
@@ -1767,7 +1767,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
-        <v>1887</v>
+        <v>1894</v>
       </c>
       <c r="B45" t="s">
         <v>36</v>
@@ -2151,66 +2151,66 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
-        <v>1076</v>
+        <v>1089</v>
       </c>
       <c r="B93" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="B94" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="B95" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="B96" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B97" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="B98" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="B99" t="s">
-        <v>233</v>
+        <v>84</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="B100" t="s">
-        <v>113</v>
+        <v>233</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
@@ -2391,18 +2391,18 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B123" t="s">
-        <v>107</v>
+        <v>235</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="B124" t="s">
-        <v>235</v>
+        <v>107</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
@@ -2471,7 +2471,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
-        <v>7325</v>
+        <v>7326</v>
       </c>
       <c r="B133" t="s">
         <v>118</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
-        <v>4854</v>
+        <v>4858</v>
       </c>
       <c r="B136" t="s">
         <v>121</v>
@@ -2519,7 +2519,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
-        <v>4659</v>
+        <v>4682</v>
       </c>
       <c r="B139" t="s">
         <v>124</v>
@@ -2543,7 +2543,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
-        <v>3684</v>
+        <v>3688</v>
       </c>
       <c r="B142" t="s">
         <v>127</v>
@@ -2559,7 +2559,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
-        <v>3627</v>
+        <v>3640</v>
       </c>
       <c r="B144" t="s">
         <v>129</v>
@@ -2575,31 +2575,31 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
-        <v>3178</v>
+        <v>3267</v>
       </c>
       <c r="B146" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
-        <v>3168</v>
+        <v>3208</v>
       </c>
       <c r="B147" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
-        <v>3109</v>
+        <v>3178</v>
       </c>
       <c r="B148" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
-        <v>3057</v>
+        <v>3156</v>
       </c>
       <c r="B149" t="s">
         <v>134</v>
@@ -2607,7 +2607,7 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
-        <v>2975</v>
+        <v>3074</v>
       </c>
       <c r="B150" t="s">
         <v>135</v>
@@ -2615,34 +2615,34 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
-        <v>2923</v>
+        <v>3007</v>
       </c>
       <c r="B151" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
-        <v>2908</v>
+        <v>2923</v>
       </c>
       <c r="B152" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
-        <v>2852</v>
+        <v>2857</v>
       </c>
       <c r="B153" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
-        <v>2758</v>
+        <v>2852</v>
       </c>
       <c r="B154" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
@@ -2695,18 +2695,18 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
-        <v>1878</v>
+        <v>1893</v>
       </c>
       <c r="B161" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
-        <v>1851</v>
+        <v>1878</v>
       </c>
       <c r="B162" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
@@ -2879,7 +2879,7 @@
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
-        <v>2536</v>
+        <v>2539</v>
       </c>
       <c r="B184" t="s">
         <v>170</v>
@@ -2911,7 +2911,7 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
-        <v>1548</v>
+        <v>1587</v>
       </c>
       <c r="B188" t="s">
         <v>173</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="B202" t="s">
         <v>187</v>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
-        <v>4682</v>
+        <v>4684</v>
       </c>
       <c r="B218" t="s">
         <v>294</v>
@@ -3175,18 +3175,18 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
-        <v>3804</v>
+        <v>3864</v>
       </c>
       <c r="B221" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
-        <v>3788</v>
+        <v>3808</v>
       </c>
       <c r="B222" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
@@ -3223,7 +3223,7 @@
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
-        <v>3046</v>
+        <v>3050</v>
       </c>
       <c r="B227" t="s">
         <v>270</v>
@@ -3247,7 +3247,7 @@
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
-        <v>2799</v>
+        <v>2814</v>
       </c>
       <c r="B230" t="s">
         <v>266</v>
@@ -3399,26 +3399,26 @@
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
-        <v>1501</v>
+        <v>1518</v>
       </c>
       <c r="B249" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
-        <v>1500</v>
+        <v>1514</v>
       </c>
       <c r="B250" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
-        <v>1448</v>
+        <v>1501</v>
       </c>
       <c r="B251" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
@@ -3487,18 +3487,18 @@
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
-        <v>976</v>
+        <v>992</v>
       </c>
       <c r="B260" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
-        <v>959</v>
+        <v>976</v>
       </c>
       <c r="B261" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
@@ -3543,7 +3543,7 @@
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
-        <v>3234</v>
+        <v>3252</v>
       </c>
       <c r="B267" t="s">
         <v>200</v>
@@ -3591,7 +3591,7 @@
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
-        <v>2606</v>
+        <v>2613</v>
       </c>
       <c r="B273" t="s">
         <v>205</v>
@@ -3631,7 +3631,7 @@
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
-        <v>1417</v>
+        <v>1424</v>
       </c>
       <c r="B278" t="s">
         <v>210</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
-        <v>1024</v>
+        <v>1037</v>
       </c>
       <c r="B280" t="s">
         <v>213</v>
